--- a/002/002_SISMO_VIENTO_SALVADOR_3.0.xlsx
+++ b/002/002_SISMO_VIENTO_SALVADOR_3.0.xlsx
@@ -6480,7 +6480,7 @@
         <v>68</v>
       </c>
       <c r="F137" s="36">
-        <v>0.6197</v>
+        <v>0.61943</v>
       </c>
       <c r="G137" t="s">
         <v>66</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F139" s="52">
         <f>P33*Q85*P55/P99*(P57/MAX(P57,MIN(F137,6*P57)))^(2/3)</f>
-        <v>0.167775950868938</v>
+        <v>0.167824701296998</v>
       </c>
     </row>
     <row r="140" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F143" s="54">
         <f>MAX(F141,F139)</f>
-        <v>0.167775950868938</v>
+        <v>0.167824701296998</v>
       </c>
     </row>
     <row r="148" spans="2:25" s="39" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -6635,14 +6635,14 @@
         <v>87</v>
       </c>
       <c r="E165" s="82">
-        <v>12373.14</v>
+        <v>12418.39</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G165" s="55">
         <f>E165/1000</f>
-        <v>12.37314</v>
+        <v>12.41839</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>86</v>
@@ -6653,14 +6653,14 @@
         <v>88</v>
       </c>
       <c r="E166" s="82">
-        <v>12373.14</v>
+        <v>12418.39</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G166" s="55">
         <f>E166/1000</f>
-        <v>12.37314</v>
+        <v>12.41839</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>86</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G170" s="51">
         <f>G168*G165</f>
-        <v>2.12110971428571</v>
+        <v>2.12886685714286</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>86</v>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G171" s="51">
         <f>G168*G166</f>
-        <v>2.12110971428571</v>
+        <v>2.12886685714286</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>86</v>
@@ -6829,10 +6829,10 @@
         <v>1.614</v>
       </c>
       <c r="D177" s="64">
-        <v>0.6197</v>
+        <v>0.61943</v>
       </c>
       <c r="E177" s="28">
-        <v>82.16</v>
+        <v>81.83</v>
       </c>
       <c r="F177" s="28">
         <v>0</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="K177" s="32">
         <f>J177*$K$222*E177/100</f>
-        <v>1705.02180518187</v>
+        <v>1704.38391094436</v>
       </c>
       <c r="L177" s="34">
         <f>J177*$K$223*G177/100</f>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="K179" s="32">
         <f t="shared" ref="K179" si="3">J179*$K$222*E179/100</f>
-        <v>0.424221942857143</v>
+        <v>0.425773371428572</v>
       </c>
       <c r="L179" s="34">
         <f t="shared" ref="L179" si="4">J179*$K$223*G179/100</f>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="K181" s="32">
         <f t="shared" si="7"/>
-        <v>0.212110971428572</v>
+        <v>0.212886685714286</v>
       </c>
       <c r="L181" s="34">
         <f t="shared" si="8"/>
@@ -7047,13 +7047,13 @@
         <v>6</v>
       </c>
       <c r="C182" s="28">
-        <v>2.473</v>
+        <v>2.454</v>
       </c>
       <c r="D182" s="64">
-        <v>0.40443</v>
+        <v>0.40757</v>
       </c>
       <c r="E182" s="28">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="F182" s="28">
         <v>0</v>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="I182" s="29">
         <f t="shared" si="5"/>
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J182" s="31">
         <f t="shared" si="6"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K182" s="32">
         <f t="shared" si="7"/>
-        <v>104.146486971429</v>
+        <v>103.888702628571</v>
       </c>
       <c r="L182" s="34">
         <f t="shared" si="8"/>
@@ -7088,10 +7088,10 @@
         <v>7</v>
       </c>
       <c r="C183" s="28">
-        <v>2.689</v>
+        <v>2.614</v>
       </c>
       <c r="D183" s="64">
-        <v>0.37184</v>
+        <v>0.38249</v>
       </c>
       <c r="E183" s="28">
         <v>0</v>
@@ -7100,14 +7100,14 @@
         <v>0</v>
       </c>
       <c r="G183" s="28">
-        <v>88.92</v>
+        <v>88.23</v>
       </c>
       <c r="H183" s="28" t="s">
         <v>113</v>
       </c>
       <c r="I183" s="29">
         <f t="shared" si="5"/>
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J183" s="31">
         <f t="shared" si="6"/>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="L183" s="34">
         <f t="shared" si="8"/>
-        <v>1886.09075794286</v>
+        <v>1878.29922805714</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="26"/>
@@ -7129,10 +7129,10 @@
         <v>8</v>
       </c>
       <c r="C184" s="28">
-        <v>3.362</v>
+        <v>3.445</v>
       </c>
       <c r="D184" s="64">
-        <v>0.29747</v>
+        <v>0.29029</v>
       </c>
       <c r="E184" s="28">
         <v>0</v>
@@ -7141,14 +7141,14 @@
         <v>0</v>
       </c>
       <c r="G184" s="28">
-        <v>0.05</v>
+        <v>1.14</v>
       </c>
       <c r="H184" s="28" t="s">
         <v>113</v>
       </c>
       <c r="I184" s="29">
         <f t="shared" si="5"/>
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="J184" s="31">
         <f t="shared" si="6"/>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="L184" s="34">
         <f t="shared" si="8"/>
-        <v>1.06055485714286</v>
+        <v>24.2690821714286</v>
       </c>
       <c r="N184" s="10"/>
       <c r="O184" s="26"/>
@@ -7170,13 +7170,13 @@
         <v>9</v>
       </c>
       <c r="C185" s="28">
-        <v>3.529</v>
+        <v>3.552</v>
       </c>
       <c r="D185" s="64">
-        <v>0.28334</v>
+        <v>0.28157</v>
       </c>
       <c r="E185" s="28">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="F185" s="28">
         <v>0</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="K185" s="32">
         <f t="shared" si="7"/>
-        <v>1.06055485714286</v>
+        <v>1.91598017142857</v>
       </c>
       <c r="L185" s="34">
         <f t="shared" si="8"/>
@@ -7429,13 +7429,13 @@
         <v>14</v>
       </c>
       <c r="C190" s="28">
-        <v>4.426</v>
+        <v>4.435</v>
       </c>
       <c r="D190" s="64">
-        <v>0.22592</v>
+        <v>0.22546</v>
       </c>
       <c r="E190" s="28">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F190" s="28">
         <v>0</v>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="K190" s="32">
         <f t="shared" si="7"/>
-        <v>0.424221942857143</v>
+        <v>0.638660057142857</v>
       </c>
       <c r="L190" s="34">
         <f t="shared" si="8"/>
@@ -7493,10 +7493,10 @@
         <v>15</v>
       </c>
       <c r="C191" s="28">
-        <v>4.447</v>
+        <v>4.49</v>
       </c>
       <c r="D191" s="64">
-        <v>0.22486</v>
+        <v>0.22272</v>
       </c>
       <c r="E191" s="28">
         <v>0</v>
@@ -7505,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="G191" s="28">
-        <v>4.46</v>
+        <v>5.03</v>
       </c>
       <c r="H191" s="28" t="s">
         <v>113</v>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="L191" s="34">
         <f t="shared" si="8"/>
-        <v>94.6014932571429</v>
+        <v>107.082002914286</v>
       </c>
       <c r="N191" s="10"/>
       <c r="T191">
@@ -7557,10 +7557,10 @@
         <v>16</v>
       </c>
       <c r="C192" s="28">
-        <v>4.736</v>
+        <v>4.773</v>
       </c>
       <c r="D192" s="64">
-        <v>0.21116</v>
+        <v>0.20952</v>
       </c>
       <c r="E192" s="28">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G192" s="28">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="H192" s="28" t="s">
         <v>113</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="L192" s="34">
         <f t="shared" si="8"/>
-        <v>4.66644137142857</v>
+        <v>3.19330028571429</v>
       </c>
       <c r="N192" s="10"/>
       <c r="T192">
@@ -7747,10 +7747,10 @@
         <v>19</v>
       </c>
       <c r="C195" s="28">
-        <v>5.402</v>
+        <v>5.403</v>
       </c>
       <c r="D195" s="64">
-        <v>0.18511</v>
+        <v>0.18508</v>
       </c>
       <c r="E195" s="28">
         <v>0.36</v>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="K195" s="32">
         <f t="shared" si="7"/>
-        <v>7.38146180571429</v>
+        <v>7.40845666285714</v>
       </c>
       <c r="L195" s="34">
         <f t="shared" si="8"/>
@@ -7810,10 +7810,10 @@
         <v>20</v>
       </c>
       <c r="C196" s="28">
-        <v>7.292</v>
+        <v>7.291</v>
       </c>
       <c r="D196" s="64">
-        <v>0.13713</v>
+        <v>0.13715</v>
       </c>
       <c r="E196" s="28">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="G196" s="28">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="H196" s="28" t="s">
         <v>113</v>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="L196" s="34">
         <f t="shared" si="8"/>
-        <v>4.75128576</v>
+        <v>2.89525892571429</v>
       </c>
       <c r="T196">
         <v>7</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L197" s="34">
         <f t="shared" si="8"/>
-        <v>0.162618411428571</v>
+        <v>0.163213125714286</v>
       </c>
       <c r="T197">
         <v>8</v>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="L198" s="34">
         <f t="shared" si="8"/>
-        <v>0.325236822857143</v>
+        <v>0.326426251428571</v>
       </c>
       <c r="T198">
         <v>10</v>
@@ -7999,10 +7999,10 @@
         <v>23</v>
       </c>
       <c r="C199" s="28">
-        <v>7.749</v>
+        <v>7.789</v>
       </c>
       <c r="D199" s="64">
-        <v>0.12905</v>
+        <v>0.12838</v>
       </c>
       <c r="E199" s="28">
         <v>0.01</v>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="K199" s="32">
         <f t="shared" si="7"/>
-        <v>0.162618411428571</v>
+        <v>0.163213125714286</v>
       </c>
       <c r="L199" s="34">
         <f t="shared" si="8"/>
@@ -8062,10 +8062,10 @@
         <v>24</v>
       </c>
       <c r="C200" s="28">
-        <v>8.491</v>
+        <v>8.58</v>
       </c>
       <c r="D200" s="64">
-        <v>0.11778</v>
+        <v>0.11655</v>
       </c>
       <c r="E200" s="28">
         <v>0.01</v>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K200" s="32">
         <f t="shared" si="7"/>
-        <v>0.155548045714286</v>
+        <v>0.156116902857143</v>
       </c>
       <c r="L200" s="34">
         <f t="shared" si="8"/>
@@ -8125,10 +8125,10 @@
         <v>25</v>
       </c>
       <c r="C201" s="28">
-        <v>9.086</v>
+        <v>9.068</v>
       </c>
       <c r="D201" s="64">
-        <v>0.11006</v>
+        <v>0.11028</v>
       </c>
       <c r="E201" s="28">
         <v>0</v>
@@ -8188,10 +8188,10 @@
         <v>26</v>
       </c>
       <c r="C202" s="28">
-        <v>9.706</v>
+        <v>9.714</v>
       </c>
       <c r="D202" s="64">
-        <v>0.10303</v>
+        <v>0.10294</v>
       </c>
       <c r="E202" s="28">
         <v>0</v>
@@ -8200,7 +8200,7 @@
         <v>0</v>
       </c>
       <c r="G202" s="28">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H202" s="28" t="s">
         <v>113</v>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="L202" s="34">
         <f t="shared" si="8"/>
-        <v>0.282814628571429</v>
+        <v>0</v>
       </c>
       <c r="T202">
         <v>17</v>
@@ -8251,10 +8251,10 @@
         <v>27</v>
       </c>
       <c r="C203" s="28">
-        <v>9.714</v>
+        <v>9.739</v>
       </c>
       <c r="D203" s="64">
-        <v>0.10294</v>
+        <v>0.10268</v>
       </c>
       <c r="E203" s="28">
         <v>0</v>
@@ -8263,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="G203" s="28">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H203" s="28" t="s">
         <v>113</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="L203" s="34">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.141924457142857</v>
       </c>
       <c r="T203">
         <v>18</v>
@@ -8314,10 +8314,10 @@
         <v>28</v>
       </c>
       <c r="C204" s="28">
-        <v>9.824</v>
+        <v>9.888</v>
       </c>
       <c r="D204" s="64">
-        <v>0.10179</v>
+        <v>0.10113</v>
       </c>
       <c r="E204" s="28">
         <v>0</v>
@@ -8326,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="G204" s="28">
-        <v>1.74</v>
+        <v>1.13</v>
       </c>
       <c r="H204" s="28" t="s">
         <v>113</v>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="L204" s="34">
         <f t="shared" si="8"/>
-        <v>24.6048726857143</v>
+        <v>16.0374636571429</v>
       </c>
       <c r="P204" s="38"/>
       <c r="T204">
@@ -8378,13 +8378,13 @@
         <v>29</v>
       </c>
       <c r="C205" s="28">
-        <v>10.083</v>
+        <v>10.054</v>
       </c>
       <c r="D205" s="64">
-        <v>0.09917</v>
+        <v>0.09947</v>
       </c>
       <c r="E205" s="28">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F205" s="28">
         <v>0</v>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="K205" s="32">
         <f t="shared" si="7"/>
-        <v>0.424221942857143</v>
+        <v>0.283848914285714</v>
       </c>
       <c r="L205" s="34">
         <f t="shared" si="8"/>
@@ -8447,7 +8447,7 @@
         <v>0.09807</v>
       </c>
       <c r="E206" s="28">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="F206" s="28">
         <v>0</v>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="K206" s="32">
         <f t="shared" si="7"/>
-        <v>49.0683380571429</v>
+        <v>49.5316355428571</v>
       </c>
       <c r="L206" s="34">
         <f t="shared" si="8"/>
@@ -8633,7 +8633,7 @@
         <v>11.407</v>
       </c>
       <c r="D209" s="64">
-        <v>0.08767</v>
+        <v>0.08766</v>
       </c>
       <c r="E209" s="28">
         <v>0</v>
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="G209" s="28">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H209" s="28" t="s">
         <v>113</v>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="L209" s="34">
         <f t="shared" si="8"/>
-        <v>2.82107592</v>
+        <v>3.10104938857143</v>
       </c>
       <c r="T209">
         <v>24</v>
@@ -8759,7 +8759,7 @@
         <v>11.496</v>
       </c>
       <c r="D211" s="64">
-        <v>0.08698</v>
+        <v>0.08699</v>
       </c>
       <c r="E211" s="28">
         <v>0.77</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="K211" s="32">
         <f t="shared" si="7"/>
-        <v>10.34394504</v>
+        <v>10.38177404</v>
       </c>
       <c r="L211" s="34">
         <f t="shared" si="8"/>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="K213" s="32">
         <f t="shared" si="7"/>
-        <v>1.88071728</v>
+        <v>1.88759528</v>
       </c>
       <c r="L213" s="34">
         <f t="shared" si="8"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="K215" s="32">
         <f t="shared" si="7"/>
-        <v>0.806021691428571</v>
+        <v>0.808969405714286</v>
       </c>
       <c r="L215" s="34">
         <f t="shared" si="8"/>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="K217" s="32">
         <f t="shared" si="7"/>
-        <v>0.134336948571429</v>
+        <v>0.134828234285714</v>
       </c>
       <c r="L217" s="34">
         <f t="shared" si="8"/>
@@ -9326,7 +9326,7 @@
       <c r="D220" s="115"/>
       <c r="E220" s="116">
         <f>SUM(E177:E219)</f>
-        <v>92.03</v>
+        <v>91.73</v>
       </c>
       <c r="F220" s="116">
         <f t="shared" ref="F220" si="9">SUM(F177:F219)</f>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="G220" s="116">
         <f>SUM(G177:G219)</f>
-        <v>95.93</v>
+        <v>96.12</v>
       </c>
       <c r="H220" s="140" t="s">
         <v>131</v>
@@ -9343,11 +9343,11 @@
       <c r="J220" s="142"/>
       <c r="K220" s="117">
         <f>SQRT(SUMSQ(K177:K219))</f>
-        <v>1708.95318747661</v>
+        <v>1708.31557403176</v>
       </c>
       <c r="L220" s="117">
         <f>SQRT(SUMSQ(L177:L219))</f>
-        <v>1888.63623689928</v>
+        <v>1881.58153785363</v>
       </c>
       <c r="T220">
         <v>52</v>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="K222" s="30">
         <f>E165</f>
-        <v>12373.14</v>
+        <v>12418.39</v>
       </c>
       <c r="L222" t="s">
         <v>134</v>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="K223" s="30">
         <f>E166</f>
-        <v>12373.14</v>
+        <v>12418.39</v>
       </c>
       <c r="L223" t="s">
         <v>134</v>
@@ -9515,11 +9515,11 @@
       </c>
       <c r="K225" s="30">
         <f>K222*VLOOKUP(MAX(E177:E219),E177:J219,6,0)</f>
-        <v>2075.2456246128</v>
+        <v>2082.8350372044</v>
       </c>
       <c r="L225" s="30">
         <f>K222*VLOOKUP(MAX(G177:G219),G177:J219,4,0)</f>
-        <v>2121.10971428571</v>
+        <v>2128.86685714286</v>
       </c>
       <c r="T225">
         <v>57</v>
@@ -9552,11 +9552,11 @@
       </c>
       <c r="K226" s="30">
         <f>0.9*K225</f>
-        <v>1867.72106215152</v>
+        <v>1874.55153348396</v>
       </c>
       <c r="L226" s="30">
         <f>0.9*L225</f>
-        <v>1908.99874285714</v>
+        <v>1915.98017142857</v>
       </c>
       <c r="T226">
         <v>58</v>
@@ -9621,11 +9621,11 @@
       </c>
       <c r="K228" s="30">
         <f>K222*G168</f>
-        <v>2121.10971428571</v>
+        <v>2128.86685714286</v>
       </c>
       <c r="L228" s="30">
         <f>K222*G168</f>
-        <v>2121.10971428571</v>
+        <v>2128.86685714286</v>
       </c>
       <c r="T228">
         <v>60</v>
@@ -9658,11 +9658,11 @@
       </c>
       <c r="K229" s="30">
         <f>0.8*K228</f>
-        <v>1696.88777142857</v>
+        <v>1703.09348571429</v>
       </c>
       <c r="L229" s="30">
         <f>0.8*L228</f>
-        <v>1696.88777142857</v>
+        <v>1703.09348571429</v>
       </c>
       <c r="T229">
         <v>61</v>
@@ -9751,11 +9751,11 @@
       </c>
       <c r="K232" s="44">
         <f>MAX(K229,K226)</f>
-        <v>1867.72106215152</v>
+        <v>1874.55153348396</v>
       </c>
       <c r="L232" s="44">
         <f>MAX(L229,L226)</f>
-        <v>1908.99874285714</v>
+        <v>1915.98017142857</v>
       </c>
       <c r="T232">
         <v>64</v>
@@ -9877,11 +9877,11 @@
       </c>
       <c r="K236" s="47">
         <f>K232/1000</f>
-        <v>1.86772106215152</v>
+        <v>1.87455153348396</v>
       </c>
       <c r="L236" s="47">
         <f>L232/1000</f>
-        <v>1.90899874285714</v>
+        <v>1.91598017142857</v>
       </c>
       <c r="T236">
         <v>68</v>
@@ -9914,11 +9914,11 @@
       </c>
       <c r="K237" s="47">
         <f>K220/1000</f>
-        <v>1.70895318747661</v>
+        <v>1.70831557403176</v>
       </c>
       <c r="L237" s="47">
         <f>L220/1000</f>
-        <v>1.88863623689928</v>
+        <v>1.88158153785363</v>
       </c>
       <c r="T237">
         <v>69</v>
@@ -9988,11 +9988,11 @@
       </c>
       <c r="K239" s="86">
         <f>MAX(K236/K237,1)</f>
-        <v>1.09290358322181</v>
+        <v>1.09730986591656</v>
       </c>
       <c r="L239" s="86">
         <f>MAX(L236/L237,1)</f>
-        <v>1.01078159232574</v>
+        <v>1.01828176610097</v>
       </c>
       <c r="T239">
         <v>71</v>
@@ -10051,11 +10051,11 @@
       </c>
       <c r="K241" s="86">
         <f>IF(K226/K220&lt;1,"N/A",K226/K220)</f>
-        <v>1.09290358322181</v>
+        <v>1.09730986591656</v>
       </c>
       <c r="L241" s="86">
         <f>IF(L226/L220&lt;1,"N/A",L226/L220)</f>
-        <v>1.01078159232574</v>
+        <v>1.01828176610097</v>
       </c>
       <c r="T241">
         <v>73</v>
@@ -10111,11 +10111,11 @@
     <row r="243" spans="2:27" x14ac:dyDescent="0.3">
       <c r="K243" s="53">
         <f>K225/K220</f>
-        <v>1.2143373146909</v>
+        <v>1.21923318435174</v>
       </c>
       <c r="L243" s="53">
         <f>L225/L220</f>
-        <v>1.12309065813971</v>
+        <v>1.13142418455663</v>
       </c>
       <c r="T243">
         <v>75</v>

--- a/002/002_SISMO_VIENTO_SALVADOR_3.0.xlsx
+++ b/002/002_SISMO_VIENTO_SALVADOR_3.0.xlsx
@@ -6480,7 +6480,7 @@
         <v>68</v>
       </c>
       <c r="F137" s="36">
-        <v>0.61943</v>
+        <v>0.61658</v>
       </c>
       <c r="G137" t="s">
         <v>66</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F139" s="52">
         <f>P33*Q85*P55/P99*(P57/MAX(P57,MIN(F137,6*P57)))^(2/3)</f>
-        <v>0.167824701296998</v>
+        <v>0.168341457901999</v>
       </c>
     </row>
     <row r="140" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F143" s="54">
         <f>MAX(F141,F139)</f>
-        <v>0.167824701296998</v>
+        <v>0.168341457901999</v>
       </c>
     </row>
     <row r="148" spans="2:25" s="39" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -6635,14 +6635,14 @@
         <v>87</v>
       </c>
       <c r="E165" s="82">
-        <v>12418.39</v>
+        <v>12330.62</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G165" s="55">
         <f>E165/1000</f>
-        <v>12.41839</v>
+        <v>12.33062</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>86</v>
@@ -6653,14 +6653,14 @@
         <v>88</v>
       </c>
       <c r="E166" s="82">
-        <v>12418.39</v>
+        <v>12330.62</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>85</v>
       </c>
       <c r="G166" s="55">
         <f>E166/1000</f>
-        <v>12.41839</v>
+        <v>12.33062</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>86</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G170" s="51">
         <f>G168*G165</f>
-        <v>2.12886685714286</v>
+        <v>2.11382057142857</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>86</v>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G171" s="51">
         <f>G168*G166</f>
-        <v>2.12886685714286</v>
+        <v>2.11382057142857</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>86</v>
@@ -6826,13 +6826,13 @@
         <v>1</v>
       </c>
       <c r="C177" s="28">
-        <v>1.614</v>
+        <v>1.622</v>
       </c>
       <c r="D177" s="64">
-        <v>0.61943</v>
+        <v>0.61658</v>
       </c>
       <c r="E177" s="28">
-        <v>81.83</v>
+        <v>81.76</v>
       </c>
       <c r="F177" s="28">
         <v>0</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="K177" s="32">
         <f>J177*$K$222*E177/100</f>
-        <v>1704.38391094436</v>
+        <v>1690.89008211308</v>
       </c>
       <c r="L177" s="34">
         <f>J177*$K$223*G177/100</f>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="K179" s="32">
         <f t="shared" ref="K179" si="3">J179*$K$222*E179/100</f>
-        <v>0.425773371428572</v>
+        <v>0.422764114285714</v>
       </c>
       <c r="L179" s="34">
         <f t="shared" ref="L179" si="4">J179*$K$223*G179/100</f>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="K181" s="32">
         <f t="shared" si="7"/>
-        <v>0.212886685714286</v>
+        <v>0.211382057142857</v>
       </c>
       <c r="L181" s="34">
         <f t="shared" si="8"/>
@@ -7047,13 +7047,13 @@
         <v>6</v>
       </c>
       <c r="C182" s="28">
-        <v>2.454</v>
+        <v>2.464</v>
       </c>
       <c r="D182" s="64">
-        <v>0.40757</v>
+        <v>0.40589</v>
       </c>
       <c r="E182" s="28">
-        <v>4.88</v>
+        <v>4.85</v>
       </c>
       <c r="F182" s="28">
         <v>0</v>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K182" s="32">
         <f t="shared" si="7"/>
-        <v>103.888702628571</v>
+        <v>102.520297714286</v>
       </c>
       <c r="L182" s="34">
         <f t="shared" si="8"/>
@@ -7088,10 +7088,10 @@
         <v>7</v>
       </c>
       <c r="C183" s="28">
-        <v>2.614</v>
+        <v>2.62</v>
       </c>
       <c r="D183" s="64">
-        <v>0.38249</v>
+        <v>0.38161</v>
       </c>
       <c r="E183" s="28">
         <v>0</v>
@@ -7100,7 +7100,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="28">
-        <v>88.23</v>
+        <v>88</v>
       </c>
       <c r="H183" s="28" t="s">
         <v>113</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="L183" s="34">
         <f t="shared" si="8"/>
-        <v>1878.29922805714</v>
+        <v>1860.16210285714</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="26"/>
@@ -7129,10 +7129,10 @@
         <v>8</v>
       </c>
       <c r="C184" s="28">
-        <v>3.445</v>
+        <v>3.448</v>
       </c>
       <c r="D184" s="64">
-        <v>0.29029</v>
+        <v>0.29005</v>
       </c>
       <c r="E184" s="28">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="G184" s="28">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="H184" s="28" t="s">
         <v>113</v>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="L184" s="34">
         <f t="shared" si="8"/>
-        <v>24.2690821714286</v>
+        <v>25.1544648</v>
       </c>
       <c r="N184" s="10"/>
       <c r="O184" s="26"/>
@@ -7170,10 +7170,10 @@
         <v>9</v>
       </c>
       <c r="C185" s="28">
-        <v>3.552</v>
+        <v>3.553</v>
       </c>
       <c r="D185" s="64">
-        <v>0.28157</v>
+        <v>0.28144</v>
       </c>
       <c r="E185" s="28">
         <v>0.09</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="K185" s="32">
         <f t="shared" si="7"/>
-        <v>1.91598017142857</v>
+        <v>1.90243851428571</v>
       </c>
       <c r="L185" s="34">
         <f t="shared" si="8"/>
@@ -7429,10 +7429,10 @@
         <v>14</v>
       </c>
       <c r="C190" s="28">
-        <v>4.435</v>
+        <v>4.438</v>
       </c>
       <c r="D190" s="64">
-        <v>0.22546</v>
+        <v>0.22535</v>
       </c>
       <c r="E190" s="28">
         <v>0.03</v>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="K190" s="32">
         <f t="shared" si="7"/>
-        <v>0.638660057142857</v>
+        <v>0.634146171428572</v>
       </c>
       <c r="L190" s="34">
         <f t="shared" si="8"/>
@@ -7493,10 +7493,10 @@
         <v>15</v>
       </c>
       <c r="C191" s="28">
-        <v>4.49</v>
+        <v>4.499</v>
       </c>
       <c r="D191" s="64">
-        <v>0.22272</v>
+        <v>0.22226</v>
       </c>
       <c r="E191" s="28">
         <v>0</v>
@@ -7505,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="G191" s="28">
-        <v>5.03</v>
+        <v>5.12</v>
       </c>
       <c r="H191" s="28" t="s">
         <v>113</v>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="L191" s="34">
         <f t="shared" si="8"/>
-        <v>107.082002914286</v>
+        <v>108.227613257143</v>
       </c>
       <c r="N191" s="10"/>
       <c r="T191">
@@ -7557,10 +7557,10 @@
         <v>16</v>
       </c>
       <c r="C192" s="28">
-        <v>4.773</v>
+        <v>4.775</v>
       </c>
       <c r="D192" s="64">
-        <v>0.20952</v>
+        <v>0.20942</v>
       </c>
       <c r="E192" s="28">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G192" s="28">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H192" s="28" t="s">
         <v>113</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="L192" s="34">
         <f t="shared" si="8"/>
-        <v>3.19330028571429</v>
+        <v>4.01625908571429</v>
       </c>
       <c r="N192" s="10"/>
       <c r="T192">
@@ -7747,13 +7747,13 @@
         <v>19</v>
       </c>
       <c r="C195" s="28">
-        <v>5.403</v>
+        <v>5.407</v>
       </c>
       <c r="D195" s="64">
-        <v>0.18508</v>
+        <v>0.18495</v>
       </c>
       <c r="E195" s="28">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="F195" s="28">
         <v>0</v>
@@ -7766,15 +7766,15 @@
       </c>
       <c r="I195" s="29">
         <f t="shared" si="5"/>
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J195" s="31">
         <f t="shared" si="6"/>
-        <v>0.165714285714286</v>
+        <v>0.16</v>
       </c>
       <c r="K195" s="32">
         <f t="shared" si="7"/>
-        <v>7.40845666285714</v>
+        <v>7.29972704</v>
       </c>
       <c r="L195" s="34">
         <f t="shared" si="8"/>
@@ -7810,10 +7810,10 @@
         <v>20</v>
       </c>
       <c r="C196" s="28">
-        <v>7.291</v>
+        <v>7.292</v>
       </c>
       <c r="D196" s="64">
-        <v>0.13715</v>
+        <v>0.13714</v>
       </c>
       <c r="E196" s="28">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="G196" s="28">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H196" s="28" t="s">
         <v>113</v>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="L196" s="34">
         <f t="shared" si="8"/>
-        <v>2.89525892571429</v>
+        <v>3.04390162285714</v>
       </c>
       <c r="T196">
         <v>7</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L197" s="34">
         <f t="shared" si="8"/>
-        <v>0.163213125714286</v>
+        <v>0.162059577142857</v>
       </c>
       <c r="T197">
         <v>8</v>
@@ -7936,10 +7936,10 @@
         <v>22</v>
       </c>
       <c r="C198" s="28">
-        <v>7.739</v>
+        <v>7.74</v>
       </c>
       <c r="D198" s="64">
-        <v>0.12922</v>
+        <v>0.12921</v>
       </c>
       <c r="E198" s="28">
         <v>0</v>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="L198" s="34">
         <f t="shared" si="8"/>
-        <v>0.326426251428571</v>
+        <v>0.324119154285714</v>
       </c>
       <c r="T198">
         <v>10</v>
@@ -7999,10 +7999,10 @@
         <v>23</v>
       </c>
       <c r="C199" s="28">
-        <v>7.789</v>
+        <v>7.826</v>
       </c>
       <c r="D199" s="64">
-        <v>0.12838</v>
+        <v>0.12778</v>
       </c>
       <c r="E199" s="28">
         <v>0.01</v>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="K199" s="32">
         <f t="shared" si="7"/>
-        <v>0.163213125714286</v>
+        <v>0.162059577142857</v>
       </c>
       <c r="L199" s="34">
         <f t="shared" si="8"/>
@@ -8062,10 +8062,10 @@
         <v>24</v>
       </c>
       <c r="C200" s="28">
-        <v>8.58</v>
+        <v>8.612</v>
       </c>
       <c r="D200" s="64">
-        <v>0.11655</v>
+        <v>0.11612</v>
       </c>
       <c r="E200" s="28">
         <v>0.01</v>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K200" s="32">
         <f t="shared" si="7"/>
-        <v>0.156116902857143</v>
+        <v>0.155013508571429</v>
       </c>
       <c r="L200" s="34">
         <f t="shared" si="8"/>
@@ -8125,10 +8125,10 @@
         <v>25</v>
       </c>
       <c r="C201" s="28">
-        <v>9.068</v>
+        <v>9.074</v>
       </c>
       <c r="D201" s="64">
-        <v>0.11028</v>
+        <v>0.11021</v>
       </c>
       <c r="E201" s="28">
         <v>0</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="L203" s="34">
         <f t="shared" si="8"/>
-        <v>0.141924457142857</v>
+        <v>0.140921371428571</v>
       </c>
       <c r="T203">
         <v>18</v>
@@ -8314,10 +8314,10 @@
         <v>28</v>
       </c>
       <c r="C204" s="28">
-        <v>9.888</v>
+        <v>9.889</v>
       </c>
       <c r="D204" s="64">
-        <v>0.10113</v>
+        <v>0.10112</v>
       </c>
       <c r="E204" s="28">
         <v>0</v>
@@ -8326,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="G204" s="28">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H204" s="28" t="s">
         <v>113</v>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="L204" s="34">
         <f t="shared" si="8"/>
-        <v>16.0374636571429</v>
+        <v>16.2059577142857</v>
       </c>
       <c r="P204" s="38"/>
       <c r="T204">
@@ -8378,10 +8378,10 @@
         <v>29</v>
       </c>
       <c r="C205" s="28">
-        <v>10.054</v>
+        <v>10.063</v>
       </c>
       <c r="D205" s="64">
-        <v>0.09947</v>
+        <v>0.09938</v>
       </c>
       <c r="E205" s="28">
         <v>0.02</v>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="K205" s="32">
         <f t="shared" si="7"/>
-        <v>0.283848914285714</v>
+        <v>0.281842742857143</v>
       </c>
       <c r="L205" s="34">
         <f t="shared" si="8"/>
@@ -8441,13 +8441,13 @@
         <v>30</v>
       </c>
       <c r="C206" s="28">
-        <v>10.197</v>
+        <v>10.201</v>
       </c>
       <c r="D206" s="64">
-        <v>0.09807</v>
+        <v>0.09803</v>
       </c>
       <c r="E206" s="28">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="F206" s="28">
         <v>0</v>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="K206" s="32">
         <f t="shared" si="7"/>
-        <v>49.5316355428571</v>
+        <v>49.32248</v>
       </c>
       <c r="L206" s="34">
         <f t="shared" si="8"/>
@@ -8567,10 +8567,10 @@
         <v>32</v>
       </c>
       <c r="C208" s="28">
-        <v>11.355</v>
+        <v>11.357</v>
       </c>
       <c r="D208" s="64">
-        <v>0.08807</v>
+        <v>0.08805</v>
       </c>
       <c r="E208" s="28">
         <v>0</v>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="L209" s="34">
         <f t="shared" si="8"/>
-        <v>3.10104938857143</v>
+        <v>3.07913196571429</v>
       </c>
       <c r="T209">
         <v>24</v>
@@ -8756,13 +8756,13 @@
         <v>35</v>
       </c>
       <c r="C211" s="28">
-        <v>11.496</v>
+        <v>11.497</v>
       </c>
       <c r="D211" s="64">
-        <v>0.08699</v>
+        <v>0.08698</v>
       </c>
       <c r="E211" s="28">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="F211" s="28">
         <v>0</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="K211" s="32">
         <f t="shared" si="7"/>
-        <v>10.38177404</v>
+        <v>10.4422736228571</v>
       </c>
       <c r="L211" s="34">
         <f t="shared" si="8"/>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="K213" s="32">
         <f t="shared" si="7"/>
-        <v>1.88759528</v>
+        <v>1.87425424</v>
       </c>
       <c r="L213" s="34">
         <f t="shared" si="8"/>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="K215" s="32">
         <f t="shared" si="7"/>
-        <v>0.808969405714286</v>
+        <v>0.803251817142857</v>
       </c>
       <c r="L215" s="34">
         <f t="shared" si="8"/>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="K217" s="32">
         <f t="shared" si="7"/>
-        <v>0.134828234285714</v>
+        <v>0.133875302857143</v>
       </c>
       <c r="L217" s="34">
         <f t="shared" si="8"/>
@@ -9326,7 +9326,7 @@
       <c r="D220" s="115"/>
       <c r="E220" s="116">
         <f>SUM(E177:E219)</f>
-        <v>91.73</v>
+        <v>91.66</v>
       </c>
       <c r="F220" s="116">
         <f t="shared" ref="F220" si="9">SUM(F177:F219)</f>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="G220" s="116">
         <f>SUM(G177:G219)</f>
-        <v>96.12</v>
+        <v>96.1</v>
       </c>
       <c r="H220" s="140" t="s">
         <v>131</v>
@@ -9343,11 +9343,11 @@
       <c r="J220" s="142"/>
       <c r="K220" s="117">
         <f>SQRT(SUMSQ(K177:K219))</f>
-        <v>1708.31557403176</v>
+        <v>1694.7634837572</v>
       </c>
       <c r="L220" s="117">
         <f>SQRT(SUMSQ(L177:L219))</f>
-        <v>1881.58153785363</v>
+        <v>1863.55753150935</v>
       </c>
       <c r="T220">
         <v>52</v>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="K222" s="30">
         <f>E165</f>
-        <v>12418.39</v>
+        <v>12330.62</v>
       </c>
       <c r="L222" t="s">
         <v>134</v>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="K223" s="30">
         <f>E166</f>
-        <v>12418.39</v>
+        <v>12330.62</v>
       </c>
       <c r="L223" t="s">
         <v>134</v>
@@ -9515,11 +9515,11 @@
       </c>
       <c r="K225" s="30">
         <f>K222*VLOOKUP(MAX(E177:E219),E177:J219,6,0)</f>
-        <v>2082.8350372044</v>
+        <v>2068.11409260406</v>
       </c>
       <c r="L225" s="30">
         <f>K222*VLOOKUP(MAX(G177:G219),G177:J219,4,0)</f>
-        <v>2128.86685714286</v>
+        <v>2113.82057142857</v>
       </c>
       <c r="T225">
         <v>57</v>
@@ -9552,11 +9552,11 @@
       </c>
       <c r="K226" s="30">
         <f>0.9*K225</f>
-        <v>1874.55153348396</v>
+        <v>1861.30268334366</v>
       </c>
       <c r="L226" s="30">
         <f>0.9*L225</f>
-        <v>1915.98017142857</v>
+        <v>1902.43851428571</v>
       </c>
       <c r="T226">
         <v>58</v>
@@ -9621,11 +9621,11 @@
       </c>
       <c r="K228" s="30">
         <f>K222*G168</f>
-        <v>2128.86685714286</v>
+        <v>2113.82057142857</v>
       </c>
       <c r="L228" s="30">
         <f>K222*G168</f>
-        <v>2128.86685714286</v>
+        <v>2113.82057142857</v>
       </c>
       <c r="T228">
         <v>60</v>
@@ -9658,11 +9658,11 @@
       </c>
       <c r="K229" s="30">
         <f>0.8*K228</f>
-        <v>1703.09348571429</v>
+        <v>1691.05645714286</v>
       </c>
       <c r="L229" s="30">
         <f>0.8*L228</f>
-        <v>1703.09348571429</v>
+        <v>1691.05645714286</v>
       </c>
       <c r="T229">
         <v>61</v>
@@ -9751,11 +9751,11 @@
       </c>
       <c r="K232" s="44">
         <f>MAX(K229,K226)</f>
-        <v>1874.55153348396</v>
+        <v>1861.30268334366</v>
       </c>
       <c r="L232" s="44">
         <f>MAX(L229,L226)</f>
-        <v>1915.98017142857</v>
+        <v>1902.43851428571</v>
       </c>
       <c r="T232">
         <v>64</v>
@@ -9877,11 +9877,11 @@
       </c>
       <c r="K236" s="47">
         <f>K232/1000</f>
-        <v>1.87455153348396</v>
+        <v>1.86130268334366</v>
       </c>
       <c r="L236" s="47">
         <f>L232/1000</f>
-        <v>1.91598017142857</v>
+        <v>1.90243851428571</v>
       </c>
       <c r="T236">
         <v>68</v>
@@ -9914,11 +9914,11 @@
       </c>
       <c r="K237" s="47">
         <f>K220/1000</f>
-        <v>1.70831557403176</v>
+        <v>1.6947634837572</v>
       </c>
       <c r="L237" s="47">
         <f>L220/1000</f>
-        <v>1.88158153785363</v>
+        <v>1.86355753150935</v>
       </c>
       <c r="T237">
         <v>69</v>
@@ -9988,11 +9988,11 @@
       </c>
       <c r="K239" s="86">
         <f>MAX(K236/K237,1)</f>
-        <v>1.09730986591656</v>
+        <v>1.09826692702704</v>
       </c>
       <c r="L239" s="86">
         <f>MAX(L236/L237,1)</f>
-        <v>1.01828176610097</v>
+        <v>1.02086384891207</v>
       </c>
       <c r="T239">
         <v>71</v>
@@ -10051,11 +10051,11 @@
       </c>
       <c r="K241" s="86">
         <f>IF(K226/K220&lt;1,"N/A",K226/K220)</f>
-        <v>1.09730986591656</v>
+        <v>1.09826692702704</v>
       </c>
       <c r="L241" s="86">
         <f>IF(L226/L220&lt;1,"N/A",L226/L220)</f>
-        <v>1.01828176610097</v>
+        <v>1.02086384891207</v>
       </c>
       <c r="T241">
         <v>73</v>
@@ -10111,11 +10111,11 @@
     <row r="243" spans="2:27" x14ac:dyDescent="0.3">
       <c r="K243" s="53">
         <f>K225/K220</f>
-        <v>1.21923318435174</v>
+        <v>1.2202965855856</v>
       </c>
       <c r="L243" s="53">
         <f>L225/L220</f>
-        <v>1.13142418455663</v>
+        <v>1.13429316545786</v>
       </c>
       <c r="T243">
         <v>75</v>

--- a/002/002_SISMO_VIENTO_SALVADOR_3.0.xlsx
+++ b/002/002_SISMO_VIENTO_SALVADOR_3.0.xlsx
@@ -6480,7 +6480,7 @@
         <v>68</v>
       </c>
       <c r="F137" s="36">
-        <v>0.61658</v>
+        <v>0.61669</v>
       </c>
       <c r="G137" t="s">
         <v>66</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F139" s="52">
         <f>P33*Q85*P55/P99*(P57/MAX(P57,MIN(F137,6*P57)))^(2/3)</f>
-        <v>0.168341457901999</v>
+        <v>0.168321439080101</v>
       </c>
     </row>
     <row r="140" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F143" s="54">
         <f>MAX(F141,F139)</f>
-        <v>0.168341457901999</v>
+        <v>0.168321439080101</v>
       </c>
     </row>
     <row r="148" spans="2:25" s="39" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -6829,10 +6829,10 @@
         <v>1.622</v>
       </c>
       <c r="D177" s="64">
-        <v>0.61658</v>
+        <v>0.61669</v>
       </c>
       <c r="E177" s="28">
-        <v>81.76</v>
+        <v>81.79</v>
       </c>
       <c r="F177" s="28">
         <v>0</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="K177" s="32">
         <f>J177*$K$222*E177/100</f>
-        <v>1690.89008211308</v>
+        <v>1691.51051634086</v>
       </c>
       <c r="L177" s="34">
         <f>J177*$K$223*G177/100</f>
@@ -6875,10 +6875,10 @@
         <v>2</v>
       </c>
       <c r="C178" s="28">
-        <v>2.055</v>
+        <v>2.054</v>
       </c>
       <c r="D178" s="64">
-        <v>0.4867</v>
+        <v>0.48678</v>
       </c>
       <c r="E178" s="28">
         <v>0</v>
@@ -6924,10 +6924,10 @@
         <v>3</v>
       </c>
       <c r="C179" s="28">
-        <v>2.055</v>
+        <v>2.054</v>
       </c>
       <c r="D179" s="64">
-        <v>0.4867</v>
+        <v>0.48678</v>
       </c>
       <c r="E179" s="28">
         <v>0.02</v>
@@ -6965,10 +6965,10 @@
         <v>4</v>
       </c>
       <c r="C180" s="28">
-        <v>2.324</v>
+        <v>2.323</v>
       </c>
       <c r="D180" s="64">
-        <v>0.43032</v>
+        <v>0.43039</v>
       </c>
       <c r="E180" s="28">
         <v>0</v>
@@ -7006,10 +7006,10 @@
         <v>5</v>
       </c>
       <c r="C181" s="28">
-        <v>2.324</v>
+        <v>2.323</v>
       </c>
       <c r="D181" s="64">
-        <v>0.43032</v>
+        <v>0.43039</v>
       </c>
       <c r="E181" s="28">
         <v>0.01</v>
@@ -7047,19 +7047,19 @@
         <v>6</v>
       </c>
       <c r="C182" s="28">
-        <v>2.464</v>
+        <v>2.466</v>
       </c>
       <c r="D182" s="64">
-        <v>0.40589</v>
+        <v>0.40545</v>
       </c>
       <c r="E182" s="28">
-        <v>4.85</v>
+        <v>4.83</v>
       </c>
       <c r="F182" s="28">
         <v>0</v>
       </c>
       <c r="G182" s="28">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H182" s="28" t="s">
         <v>113</v>
@@ -7074,11 +7074,11 @@
       </c>
       <c r="K182" s="32">
         <f t="shared" si="7"/>
-        <v>102.520297714286</v>
+        <v>102.0975336</v>
       </c>
       <c r="L182" s="34">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.211382057142857</v>
       </c>
       <c r="N182" s="10"/>
       <c r="O182" s="26"/>
@@ -7088,10 +7088,10 @@
         <v>7</v>
       </c>
       <c r="C183" s="28">
-        <v>2.62</v>
+        <v>2.616</v>
       </c>
       <c r="D183" s="64">
-        <v>0.38161</v>
+        <v>0.38231</v>
       </c>
       <c r="E183" s="28">
         <v>0</v>
@@ -7100,7 +7100,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="28">
-        <v>88</v>
+        <v>87.91</v>
       </c>
       <c r="H183" s="28" t="s">
         <v>113</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="L183" s="34">
         <f t="shared" si="8"/>
-        <v>1860.16210285714</v>
+        <v>1858.25966434286</v>
       </c>
       <c r="N183" s="10"/>
       <c r="O183" s="26"/>
@@ -7129,10 +7129,10 @@
         <v>8</v>
       </c>
       <c r="C184" s="28">
-        <v>3.448</v>
+        <v>3.432</v>
       </c>
       <c r="D184" s="64">
-        <v>0.29005</v>
+        <v>0.29135</v>
       </c>
       <c r="E184" s="28">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="G184" s="28">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="H184" s="28" t="s">
         <v>113</v>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="L184" s="34">
         <f t="shared" si="8"/>
-        <v>25.1544648</v>
+        <v>22.4064980571429</v>
       </c>
       <c r="N184" s="10"/>
       <c r="O184" s="26"/>
@@ -7170,10 +7170,10 @@
         <v>9</v>
       </c>
       <c r="C185" s="28">
-        <v>3.553</v>
+        <v>3.556</v>
       </c>
       <c r="D185" s="64">
-        <v>0.28144</v>
+        <v>0.28122</v>
       </c>
       <c r="E185" s="28">
         <v>0.09</v>
@@ -7213,7 +7213,7 @@
         <v>3.783</v>
       </c>
       <c r="D186" s="64">
-        <v>0.26431</v>
+        <v>0.26436</v>
       </c>
       <c r="E186" s="28">
         <v>0</v>
@@ -7253,7 +7253,7 @@
         <v>3.783</v>
       </c>
       <c r="D187" s="64">
-        <v>0.26431</v>
+        <v>0.26436</v>
       </c>
       <c r="E187" s="28">
         <v>0</v>
@@ -7295,7 +7295,7 @@
         <v>4.01</v>
       </c>
       <c r="D188" s="64">
-        <v>0.24936</v>
+        <v>0.2494</v>
       </c>
       <c r="E188" s="28">
         <v>0</v>
@@ -7359,7 +7359,7 @@
         <v>4.01</v>
       </c>
       <c r="D189" s="64">
-        <v>0.24936</v>
+        <v>0.2494</v>
       </c>
       <c r="E189" s="28">
         <v>0</v>
@@ -7429,7 +7429,7 @@
         <v>14</v>
       </c>
       <c r="C190" s="28">
-        <v>4.438</v>
+        <v>4.437</v>
       </c>
       <c r="D190" s="64">
         <v>0.22535</v>
@@ -7493,10 +7493,10 @@
         <v>15</v>
       </c>
       <c r="C191" s="28">
-        <v>4.499</v>
+        <v>4.484</v>
       </c>
       <c r="D191" s="64">
-        <v>0.22226</v>
+        <v>0.22301</v>
       </c>
       <c r="E191" s="28">
         <v>0</v>
@@ -7505,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="G191" s="28">
-        <v>5.12</v>
+        <v>5.27</v>
       </c>
       <c r="H191" s="28" t="s">
         <v>113</v>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="L191" s="34">
         <f t="shared" si="8"/>
-        <v>108.227613257143</v>
+        <v>111.398344114286</v>
       </c>
       <c r="N191" s="10"/>
       <c r="T191">
@@ -7557,10 +7557,10 @@
         <v>16</v>
       </c>
       <c r="C192" s="28">
-        <v>4.775</v>
+        <v>4.755</v>
       </c>
       <c r="D192" s="64">
-        <v>0.20942</v>
+        <v>0.2103</v>
       </c>
       <c r="E192" s="28">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G192" s="28">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="H192" s="28" t="s">
         <v>113</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="L192" s="34">
         <f t="shared" si="8"/>
-        <v>4.01625908571429</v>
+        <v>5.70731554285714</v>
       </c>
       <c r="N192" s="10"/>
       <c r="T192">
@@ -7621,10 +7621,10 @@
         <v>17</v>
       </c>
       <c r="C193" s="28">
-        <v>4.925</v>
+        <v>4.924</v>
       </c>
       <c r="D193" s="64">
-        <v>0.20304</v>
+        <v>0.20307</v>
       </c>
       <c r="E193" s="28">
         <v>0</v>
@@ -7684,10 +7684,10 @@
         <v>18</v>
       </c>
       <c r="C194" s="28">
-        <v>4.925</v>
+        <v>4.924</v>
       </c>
       <c r="D194" s="64">
-        <v>0.20304</v>
+        <v>0.20307</v>
       </c>
       <c r="E194" s="28">
         <v>0</v>
@@ -7747,10 +7747,10 @@
         <v>19</v>
       </c>
       <c r="C195" s="28">
-        <v>5.407</v>
+        <v>5.405</v>
       </c>
       <c r="D195" s="64">
-        <v>0.18495</v>
+        <v>0.18503</v>
       </c>
       <c r="E195" s="28">
         <v>0.37</v>
@@ -7766,15 +7766,15 @@
       </c>
       <c r="I195" s="29">
         <f t="shared" si="5"/>
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="J195" s="31">
         <f t="shared" si="6"/>
-        <v>0.16</v>
+        <v>0.165714285714286</v>
       </c>
       <c r="K195" s="32">
         <f t="shared" si="7"/>
-        <v>7.29972704</v>
+        <v>7.56043157714286</v>
       </c>
       <c r="L195" s="34">
         <f t="shared" si="8"/>
@@ -7810,10 +7810,10 @@
         <v>20</v>
       </c>
       <c r="C196" s="28">
-        <v>7.292</v>
+        <v>7.189</v>
       </c>
       <c r="D196" s="64">
-        <v>0.13714</v>
+        <v>0.1391</v>
       </c>
       <c r="E196" s="28">
         <v>0</v>
@@ -7873,10 +7873,10 @@
         <v>21</v>
       </c>
       <c r="C197" s="28">
-        <v>7.477</v>
+        <v>7.368</v>
       </c>
       <c r="D197" s="64">
-        <v>0.13374</v>
+        <v>0.13572</v>
       </c>
       <c r="E197" s="28">
         <v>0</v>
@@ -7892,11 +7892,11 @@
       </c>
       <c r="I197" s="29">
         <f t="shared" si="5"/>
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="J197" s="31">
         <f t="shared" si="6"/>
-        <v>0.131428571428571</v>
+        <v>0.137142857142857</v>
       </c>
       <c r="K197" s="32">
         <f t="shared" si="7"/>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L197" s="34">
         <f t="shared" si="8"/>
-        <v>0.162059577142857</v>
+        <v>0.169105645714286</v>
       </c>
       <c r="T197">
         <v>8</v>
@@ -7936,10 +7936,10 @@
         <v>22</v>
       </c>
       <c r="C198" s="28">
-        <v>7.74</v>
+        <v>7.621</v>
       </c>
       <c r="D198" s="64">
-        <v>0.12921</v>
+        <v>0.13122</v>
       </c>
       <c r="E198" s="28">
         <v>0</v>
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="G198" s="28">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H198" s="28" t="s">
         <v>113</v>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="L198" s="34">
         <f t="shared" si="8"/>
-        <v>0.324119154285714</v>
+        <v>0.486178731428571</v>
       </c>
       <c r="T198">
         <v>10</v>
@@ -7999,10 +7999,10 @@
         <v>23</v>
       </c>
       <c r="C199" s="28">
-        <v>7.826</v>
+        <v>7.834</v>
       </c>
       <c r="D199" s="64">
-        <v>0.12778</v>
+        <v>0.12764</v>
       </c>
       <c r="E199" s="28">
         <v>0.01</v>
@@ -8062,10 +8062,10 @@
         <v>24</v>
       </c>
       <c r="C200" s="28">
-        <v>8.612</v>
+        <v>8.599</v>
       </c>
       <c r="D200" s="64">
-        <v>0.11612</v>
+        <v>0.11629</v>
       </c>
       <c r="E200" s="28">
         <v>0.01</v>
@@ -8125,10 +8125,10 @@
         <v>25</v>
       </c>
       <c r="C201" s="28">
-        <v>9.074</v>
+        <v>9.011</v>
       </c>
       <c r="D201" s="64">
-        <v>0.11021</v>
+        <v>0.11098</v>
       </c>
       <c r="E201" s="28">
         <v>0</v>
@@ -8188,10 +8188,10 @@
         <v>26</v>
       </c>
       <c r="C202" s="28">
-        <v>9.714</v>
+        <v>9.405</v>
       </c>
       <c r="D202" s="64">
-        <v>0.10294</v>
+        <v>0.10633</v>
       </c>
       <c r="E202" s="28">
         <v>0</v>
@@ -8207,11 +8207,11 @@
       </c>
       <c r="I202" s="29">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J202" s="31">
         <f t="shared" si="6"/>
-        <v>0.114285714285714</v>
+        <v>0.12</v>
       </c>
       <c r="K202" s="32">
         <f t="shared" si="7"/>
@@ -8251,10 +8251,10 @@
         <v>27</v>
       </c>
       <c r="C203" s="28">
-        <v>9.739</v>
+        <v>9.642</v>
       </c>
       <c r="D203" s="64">
-        <v>0.10268</v>
+        <v>0.10371</v>
       </c>
       <c r="E203" s="28">
         <v>0</v>
@@ -8314,19 +8314,19 @@
         <v>28</v>
       </c>
       <c r="C204" s="28">
-        <v>9.889</v>
+        <v>9.864</v>
       </c>
       <c r="D204" s="64">
-        <v>0.10112</v>
+        <v>0.10138</v>
       </c>
       <c r="E204" s="28">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="F204" s="28">
         <v>0</v>
       </c>
       <c r="G204" s="28">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="H204" s="28" t="s">
         <v>113</v>
@@ -8341,11 +8341,11 @@
       </c>
       <c r="K204" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>49.0406372571429</v>
       </c>
       <c r="L204" s="34">
         <f t="shared" si="8"/>
-        <v>16.2059577142857</v>
+        <v>0</v>
       </c>
       <c r="P204" s="38"/>
       <c r="T204">
@@ -8378,19 +8378,19 @@
         <v>29</v>
       </c>
       <c r="C205" s="28">
-        <v>10.063</v>
+        <v>9.906</v>
       </c>
       <c r="D205" s="64">
-        <v>0.09938</v>
+        <v>0.10094</v>
       </c>
       <c r="E205" s="28">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F205" s="28">
         <v>0</v>
       </c>
       <c r="G205" s="28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="H205" s="28" t="s">
         <v>113</v>
@@ -8405,11 +8405,11 @@
       </c>
       <c r="K205" s="32">
         <f t="shared" si="7"/>
-        <v>0.281842742857143</v>
+        <v>0.140921371428571</v>
       </c>
       <c r="L205" s="34">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16.3468790857143</v>
       </c>
       <c r="T205">
         <v>20</v>
@@ -8441,13 +8441,13 @@
         <v>30</v>
       </c>
       <c r="C206" s="28">
-        <v>10.201</v>
+        <v>10.04</v>
       </c>
       <c r="D206" s="64">
-        <v>0.09803</v>
+        <v>0.0996</v>
       </c>
       <c r="E206" s="28">
-        <v>3.5</v>
+        <v>0.06</v>
       </c>
       <c r="F206" s="28">
         <v>0</v>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="K206" s="32">
         <f t="shared" si="7"/>
-        <v>49.32248</v>
+        <v>0.845528228571429</v>
       </c>
       <c r="L206" s="34">
         <f t="shared" si="8"/>
@@ -8504,10 +8504,10 @@
         <v>31</v>
       </c>
       <c r="C207" s="28">
-        <v>11.251</v>
+        <v>10.877</v>
       </c>
       <c r="D207" s="64">
-        <v>0.08888</v>
+        <v>0.09194</v>
       </c>
       <c r="E207" s="28">
         <v>0</v>
@@ -8567,10 +8567,10 @@
         <v>32</v>
       </c>
       <c r="C208" s="28">
-        <v>11.357</v>
+        <v>10.963</v>
       </c>
       <c r="D208" s="64">
-        <v>0.08805</v>
+        <v>0.09121</v>
       </c>
       <c r="E208" s="28">
         <v>0</v>
@@ -8630,10 +8630,10 @@
         <v>33</v>
       </c>
       <c r="C209" s="28">
-        <v>11.407</v>
+        <v>11.002</v>
       </c>
       <c r="D209" s="64">
-        <v>0.08766</v>
+        <v>0.0909</v>
       </c>
       <c r="E209" s="28">
         <v>0</v>
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="G209" s="28">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="H209" s="28" t="s">
         <v>113</v>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="L209" s="34">
         <f t="shared" si="8"/>
-        <v>3.07913196571429</v>
+        <v>0</v>
       </c>
       <c r="T209">
         <v>24</v>
@@ -8693,13 +8693,13 @@
         <v>34</v>
       </c>
       <c r="C210" s="28">
-        <v>11.457</v>
+        <v>11.05</v>
       </c>
       <c r="D210" s="64">
-        <v>0.08728</v>
+        <v>0.0905</v>
       </c>
       <c r="E210" s="28">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="F210" s="28">
         <v>0</v>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="K210" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10.30839832</v>
       </c>
       <c r="L210" s="34">
         <f t="shared" si="8"/>
@@ -8756,13 +8756,13 @@
         <v>35</v>
       </c>
       <c r="C211" s="28">
-        <v>11.497</v>
+        <v>11.111</v>
       </c>
       <c r="D211" s="64">
-        <v>0.08698</v>
+        <v>0.09</v>
       </c>
       <c r="E211" s="28">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F211" s="28">
         <v>0</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="K211" s="32">
         <f t="shared" si="7"/>
-        <v>10.4422736228571</v>
+        <v>0</v>
       </c>
       <c r="L211" s="34">
         <f t="shared" si="8"/>
@@ -8819,13 +8819,13 @@
         <v>36</v>
       </c>
       <c r="C212" s="28">
-        <v>11.581</v>
+        <v>11.121</v>
       </c>
       <c r="D212" s="64">
-        <v>0.08635</v>
+        <v>0.08992</v>
       </c>
       <c r="E212" s="28">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F212" s="28">
         <v>0</v>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="K212" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.47262833142857</v>
       </c>
       <c r="L212" s="34">
         <f t="shared" si="8"/>
@@ -8882,13 +8882,13 @@
         <v>37</v>
       </c>
       <c r="C213" s="28">
-        <v>11.585</v>
+        <v>11.13</v>
       </c>
       <c r="D213" s="64">
-        <v>0.08632</v>
+        <v>0.08985</v>
       </c>
       <c r="E213" s="28">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="F213" s="28">
         <v>0</v>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="K213" s="32">
         <f t="shared" si="7"/>
-        <v>1.87425424</v>
+        <v>0</v>
       </c>
       <c r="L213" s="34">
         <f t="shared" si="8"/>
@@ -8945,13 +8945,13 @@
         <v>38</v>
       </c>
       <c r="C214" s="28">
-        <v>11.603</v>
+        <v>11.134</v>
       </c>
       <c r="D214" s="64">
-        <v>0.08618</v>
+        <v>0.08982</v>
       </c>
       <c r="E214" s="28">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F214" s="28">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="K214" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.669376514285714</v>
       </c>
       <c r="L214" s="34">
         <f t="shared" si="8"/>
@@ -9008,13 +9008,13 @@
         <v>39</v>
       </c>
       <c r="C215" s="28">
-        <v>11.604</v>
+        <v>11.137</v>
       </c>
       <c r="D215" s="64">
-        <v>0.08617</v>
+        <v>0.08979</v>
       </c>
       <c r="E215" s="28">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="F215" s="28">
         <v>0</v>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="K215" s="32">
         <f t="shared" si="7"/>
-        <v>0.803251817142857</v>
+        <v>0</v>
       </c>
       <c r="L215" s="34">
         <f t="shared" si="8"/>
@@ -9071,10 +9071,10 @@
         <v>40</v>
       </c>
       <c r="C216" s="28">
-        <v>11.612</v>
+        <v>11.139</v>
       </c>
       <c r="D216" s="64">
-        <v>0.08612</v>
+        <v>0.08978</v>
       </c>
       <c r="E216" s="28">
         <v>0</v>
@@ -9134,13 +9134,13 @@
         <v>41</v>
       </c>
       <c r="C217" s="28">
-        <v>11.613</v>
+        <v>11.14</v>
       </c>
       <c r="D217" s="64">
-        <v>0.08611</v>
+        <v>0.08977</v>
       </c>
       <c r="E217" s="28">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F217" s="28">
         <v>0</v>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="K217" s="32">
         <f t="shared" si="7"/>
-        <v>0.133875302857143</v>
+        <v>0</v>
       </c>
       <c r="L217" s="34">
         <f t="shared" si="8"/>
@@ -9197,10 +9197,10 @@
         <v>42</v>
       </c>
       <c r="C218" s="28">
-        <v>11.617</v>
+        <v>11.141</v>
       </c>
       <c r="D218" s="64">
-        <v>0.08608</v>
+        <v>0.08976</v>
       </c>
       <c r="E218" s="28">
         <v>0</v>
@@ -9260,10 +9260,10 @@
         <v>43</v>
       </c>
       <c r="C219" s="28">
-        <v>11.617</v>
+        <v>11.216</v>
       </c>
       <c r="D219" s="64">
-        <v>0.08608</v>
+        <v>0.08916</v>
       </c>
       <c r="E219" s="28">
         <v>0</v>
@@ -9326,7 +9326,7 @@
       <c r="D220" s="115"/>
       <c r="E220" s="116">
         <f>SUM(E177:E219)</f>
-        <v>91.66</v>
+        <v>91.64</v>
       </c>
       <c r="F220" s="116">
         <f t="shared" ref="F220" si="9">SUM(F177:F219)</f>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="G220" s="116">
         <f>SUM(G177:G219)</f>
-        <v>96.1</v>
+        <v>95.91</v>
       </c>
       <c r="H220" s="140" t="s">
         <v>131</v>
@@ -9343,11 +9343,11 @@
       <c r="J220" s="142"/>
       <c r="K220" s="117">
         <f>SQRT(SUMSQ(K177:K219))</f>
-        <v>1694.7634837572</v>
+        <v>1695.34886886359</v>
       </c>
       <c r="L220" s="117">
         <f>SQRT(SUMSQ(L177:L219))</f>
-        <v>1863.55753150935</v>
+        <v>1861.81363490054</v>
       </c>
       <c r="T220">
         <v>52</v>
@@ -9914,11 +9914,11 @@
       </c>
       <c r="K237" s="47">
         <f>K220/1000</f>
-        <v>1.6947634837572</v>
+        <v>1.69534886886359</v>
       </c>
       <c r="L237" s="47">
         <f>L220/1000</f>
-        <v>1.86355753150935</v>
+        <v>1.86181363490054</v>
       </c>
       <c r="T237">
         <v>69</v>
@@ -9988,11 +9988,11 @@
       </c>
       <c r="K239" s="86">
         <f>MAX(K236/K237,1)</f>
-        <v>1.09826692702704</v>
+        <v>1.09788770767359</v>
       </c>
       <c r="L239" s="86">
         <f>MAX(L236/L237,1)</f>
-        <v>1.02086384891207</v>
+        <v>1.02182005686479</v>
       </c>
       <c r="T239">
         <v>71</v>
@@ -10051,11 +10051,11 @@
       </c>
       <c r="K241" s="86">
         <f>IF(K226/K220&lt;1,"N/A",K226/K220)</f>
-        <v>1.09826692702704</v>
+        <v>1.09788770767359</v>
       </c>
       <c r="L241" s="86">
         <f>IF(L226/L220&lt;1,"N/A",L226/L220)</f>
-        <v>1.02086384891207</v>
+        <v>1.02182005686479</v>
       </c>
       <c r="T241">
         <v>73</v>
@@ -10111,11 +10111,11 @@
     <row r="243" spans="2:27" x14ac:dyDescent="0.3">
       <c r="K243" s="53">
         <f>K225/K220</f>
-        <v>1.2202965855856</v>
+        <v>1.21987523074843</v>
       </c>
       <c r="L243" s="53">
         <f>L225/L220</f>
-        <v>1.13429316545786</v>
+        <v>1.13535561873866</v>
       </c>
       <c r="T243">
         <v>75</v>
